--- a/Result/checksun_type/軍工.xlsx
+++ b/Result/checksun_type/軍工.xlsx
@@ -641,62 +641,62 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>my_signal</t>
+          <t>up_up</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_3d</t>
+          <t>up_up_3d</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_5d</t>
+          <t>up_up_5d</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_10d</t>
+          <t>up_up_10d</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>up_up</t>
+          <t>bbw_cross</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>up_up_3d</t>
+          <t>MA_UP_d</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>up_up_5d</t>
+          <t>MA_UP_3d</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>up_up_10d</t>
+          <t>MA_UP_5d</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>bbw_cross</t>
+          <t>MA_UP_10d</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_3d</t>
+          <t>MA_UP_20d</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_5d</t>
+          <t>MA_UP_30d</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_10d</t>
+          <t>MA_UP_40d</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1893,11 +1893,15 @@
           <t>171.2</t>
         </is>
       </c>
-      <c r="CQ2" t="n">
-        <v>172.02</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>178.36</v>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>172.02</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>178.36</t>
+        </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
@@ -2650,7 +2654,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -2665,7 +2669,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -2675,12 +2679,12 @@
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -2875,11 +2879,15 @@
           <t>170.6</t>
         </is>
       </c>
-      <c r="CQ3" t="n">
-        <v>172.32</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>178.79</v>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>172.32</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>178.79</t>
+        </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
@@ -3632,7 +3640,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -3647,22 +3655,22 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -3857,11 +3865,15 @@
           <t>169.7</t>
         </is>
       </c>
-      <c r="CQ4" t="n">
-        <v>172.82</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>179.56</v>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>172.82</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>179.56</t>
+        </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
@@ -4614,7 +4626,7 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -4629,22 +4641,22 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -4839,11 +4851,15 @@
           <t>169.65</t>
         </is>
       </c>
-      <c r="CQ5" t="n">
-        <v>173.45</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>180.16</v>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>173.45</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>180.16</t>
+        </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
@@ -5596,7 +5612,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -5611,22 +5627,22 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -5821,11 +5837,15 @@
           <t>170.0</t>
         </is>
       </c>
-      <c r="CQ6" t="n">
-        <v>174.48</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>181.16</v>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>174.48</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>181.16</t>
+        </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
@@ -6578,7 +6598,7 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -6593,22 +6613,22 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -6803,11 +6823,15 @@
           <t>170.3</t>
         </is>
       </c>
-      <c r="CQ7" t="n">
-        <v>176</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>182.65</v>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>176.0</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>182.65</t>
+        </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
@@ -7560,7 +7584,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -7575,22 +7599,22 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -7785,11 +7809,15 @@
           <t>170.9</t>
         </is>
       </c>
-      <c r="CQ8" t="n">
-        <v>177.2</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>184.67</v>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>177.2</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>184.67</t>
+        </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
@@ -8542,7 +8570,7 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -8557,22 +8585,22 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -8767,11 +8795,15 @@
           <t>171.4</t>
         </is>
       </c>
-      <c r="CQ9" t="n">
-        <v>177.68</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>186.56</v>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>177.68</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>186.56</t>
+        </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
@@ -9524,7 +9556,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -9539,22 +9571,22 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -9749,11 +9781,15 @@
           <t>172.0</t>
         </is>
       </c>
-      <c r="CQ10" t="n">
-        <v>178.38</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>188.13</v>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>178.38</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>188.13</t>
+        </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
@@ -10506,7 +10542,7 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
@@ -10521,7 +10557,7 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
@@ -10531,12 +10567,12 @@
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -10731,11 +10767,15 @@
           <t>63.84</t>
         </is>
       </c>
-      <c r="CQ11" t="n">
-        <v>64.18000000000001</v>
-      </c>
-      <c r="CR11" t="n">
-        <v>64.81999999999999</v>
+      <c r="CQ11" t="inlineStr">
+        <is>
+          <t>64.18</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>64.82</t>
+        </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
@@ -11488,7 +11528,7 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
@@ -11503,7 +11543,7 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
@@ -11513,12 +11553,12 @@
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -11713,11 +11753,15 @@
           <t>63.73999999999999</t>
         </is>
       </c>
-      <c r="CQ12" t="n">
-        <v>64.20999999999999</v>
-      </c>
-      <c r="CR12" t="n">
-        <v>64.79000000000001</v>
+      <c r="CQ12" t="inlineStr">
+        <is>
+          <t>64.21</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
+          <t>64.79</t>
+        </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
@@ -12470,7 +12514,7 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
@@ -12485,22 +12529,22 @@
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -12695,11 +12739,15 @@
           <t>63.5</t>
         </is>
       </c>
-      <c r="CQ13" t="n">
-        <v>64.34</v>
-      </c>
-      <c r="CR13" t="n">
-        <v>64.93000000000001</v>
+      <c r="CQ13" t="inlineStr">
+        <is>
+          <t>64.34</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
+          <t>64.93</t>
+        </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
@@ -13452,7 +13500,7 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
@@ -13467,22 +13515,22 @@
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
@@ -13677,11 +13725,15 @@
           <t>63.48</t>
         </is>
       </c>
-      <c r="CQ14" t="n">
-        <v>64.48</v>
-      </c>
-      <c r="CR14" t="n">
-        <v>64.95</v>
+      <c r="CQ14" t="inlineStr">
+        <is>
+          <t>64.48</t>
+        </is>
+      </c>
+      <c r="CR14" t="inlineStr">
+        <is>
+          <t>64.95</t>
+        </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
@@ -14434,7 +14486,7 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
@@ -14449,22 +14501,22 @@
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -14659,11 +14711,15 @@
           <t>63.55</t>
         </is>
       </c>
-      <c r="CQ15" t="n">
-        <v>64.72</v>
-      </c>
-      <c r="CR15" t="n">
-        <v>64.91</v>
+      <c r="CQ15" t="inlineStr">
+        <is>
+          <t>64.72</t>
+        </is>
+      </c>
+      <c r="CR15" t="inlineStr">
+        <is>
+          <t>64.91</t>
+        </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
@@ -15416,7 +15472,7 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
@@ -15431,22 +15487,22 @@
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -15641,11 +15697,15 @@
           <t>63.62</t>
         </is>
       </c>
-      <c r="CQ16" t="n">
-        <v>65.08</v>
-      </c>
-      <c r="CR16" t="n">
-        <v>64.94</v>
+      <c r="CQ16" t="inlineStr">
+        <is>
+          <t>65.08</t>
+        </is>
+      </c>
+      <c r="CR16" t="inlineStr">
+        <is>
+          <t>64.94</t>
+        </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
@@ -16398,7 +16458,7 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
@@ -16413,22 +16473,22 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -16623,11 +16683,15 @@
           <t>63.9</t>
         </is>
       </c>
-      <c r="CQ17" t="n">
-        <v>65.40000000000001</v>
-      </c>
-      <c r="CR17" t="n">
-        <v>65.06</v>
+      <c r="CQ17" t="inlineStr">
+        <is>
+          <t>65.4</t>
+        </is>
+      </c>
+      <c r="CR17" t="inlineStr">
+        <is>
+          <t>65.06</t>
+        </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
@@ -17380,7 +17444,7 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
@@ -17395,22 +17459,22 @@
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -17605,11 +17669,15 @@
           <t>64.17999999999999</t>
         </is>
       </c>
-      <c r="CQ18" t="n">
-        <v>65.58</v>
-      </c>
-      <c r="CR18" t="n">
-        <v>65.14</v>
+      <c r="CQ18" t="inlineStr">
+        <is>
+          <t>65.58</t>
+        </is>
+      </c>
+      <c r="CR18" t="inlineStr">
+        <is>
+          <t>65.14</t>
+        </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
@@ -18362,7 +18430,7 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
@@ -18377,22 +18445,22 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -18587,11 +18655,15 @@
           <t>64.43999999999998</t>
         </is>
       </c>
-      <c r="CQ19" t="n">
-        <v>65.81999999999999</v>
-      </c>
-      <c r="CR19" t="n">
-        <v>65.14</v>
+      <c r="CQ19" t="inlineStr">
+        <is>
+          <t>65.82</t>
+        </is>
+      </c>
+      <c r="CR19" t="inlineStr">
+        <is>
+          <t>65.14</t>
+        </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>

--- a/Result/checksun_type/軍工.xlsx
+++ b/Result/checksun_type/軍工.xlsx
@@ -1223,12 +1223,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3170.808</t>
+          <t>2869.332</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1238,562 +1238,562 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>156.5</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>-0.73</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>2026-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>弱勢</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>弱勢</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>18.8</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>C2 循環・中段</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>中段</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>業外占比&gt;50% / 毛利率連2季低於8季均</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>-53618.0</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>2026-09-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>5.41</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>192.0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>152.5</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>3171</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>18.63</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>-1.20</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>-4.38</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>-4.39</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>-5.42</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>165.65</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>173.25</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>-0.00814026299311199</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>-0.006218905472636815</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>-0.003758833258156624</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>-8.99</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>-4.32</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>-3.97</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>2026/09/30</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>1563422357.758197</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>448841982.0</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>292369747.8</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>280047222.6</t>
+        </is>
+      </c>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>307595241.6666667</t>
+        </is>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>736577376.64</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>-41344815.53053302</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>2026/07/03</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>-23.47</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>雷虎</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>雷虎</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>-33.24457817645055</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>27.91049322280965</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>14.8350157059527</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>7.92</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>335.42</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>35.54</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>0.10</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>71.41</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>26505</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>無人載具暨模型產品51.59%、口腔醫療器材25.92%、無菌包材18.42%、其他2.98%、鋁船1.08% (2025年)</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>雷虎-其他-上市</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>其他右上上市</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
           <t>161.0</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>-1.81</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>37.33333333333334</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>2026-08-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>弱勢</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>弱勢</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>18.8</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>C2 循環・中段</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>中段</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>35.0</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>業外占比&gt;50% / 毛利率連2季低於8季均</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>-852182.0</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>0.29</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>2026-09-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>5.98</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0.34</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
+      <c r="DN2" t="inlineStr">
         <is>
           <t>152.5</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>1022</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>18.63</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>0.81</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>-3.95</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>-4.52</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>-5.12</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>166.28</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>174.15</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>0.001253918495297768</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>-0.002171889543903127</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>-0.002250225022502272</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>-7.75</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>-4.18</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>-3.88</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>2026/09/30</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>1565861150.593151</t>
-        </is>
-      </c>
-      <c r="CH2" t="inlineStr">
-        <is>
-          <t>509244108.0</t>
-        </is>
-      </c>
-      <c r="CI2" t="inlineStr">
-        <is>
-          <t>234539382.2</t>
-        </is>
-      </c>
-      <c r="CJ2" t="inlineStr">
-        <is>
-          <t>253188397.8</t>
-        </is>
-      </c>
-      <c r="CK2" t="inlineStr">
-        <is>
-          <t>343595526.6</t>
-        </is>
-      </c>
-      <c r="CL2" t="inlineStr">
-        <is>
-          <t>792942420.6</t>
-        </is>
-      </c>
-      <c r="CM2" t="inlineStr">
-        <is>
-          <t>-48482412.48764507</t>
-        </is>
-      </c>
-      <c r="CN2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CO2" t="inlineStr">
-        <is>
-          <t>2026/07/03</t>
-        </is>
-      </c>
-      <c r="CP2" t="inlineStr">
-        <is>
-          <t>-21.27</t>
-        </is>
-      </c>
-      <c r="CQ2" t="inlineStr">
-        <is>
-          <t>雷虎</t>
-        </is>
-      </c>
-      <c r="CR2" t="inlineStr">
-        <is>
-          <t>雷虎</t>
-        </is>
-      </c>
-      <c r="CS2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="CT2" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="CU2" t="inlineStr">
-        <is>
-          <t>0.86</t>
-        </is>
-      </c>
-      <c r="CV2" t="inlineStr">
-        <is>
-          <t>-33.24457817645055</t>
-        </is>
-      </c>
-      <c r="CW2" t="inlineStr">
-        <is>
-          <t>27.91049322280965</t>
-        </is>
-      </c>
-      <c r="CX2" t="inlineStr">
-        <is>
-          <t>14.8350157059527</t>
-        </is>
-      </c>
-      <c r="CY2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>8.14</t>
-        </is>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>2.82</t>
-        </is>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>330.21</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>35.54</t>
-        </is>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>0.10</t>
-        </is>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>72.46</t>
-        </is>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>26094</t>
-        </is>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>無人載具暨模型產品51.59%、口腔醫療器材25.92%、無菌包材18.42%、其他2.98%、鋁船1.08% (2025年)</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>雷虎-其他-上市</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>其他右上上市</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>163.0</t>
-        </is>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>163.0</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>158.5</t>
-        </is>
-      </c>
       <c r="DO2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>156.5</t>
         </is>
       </c>
       <c r="DP2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1021.557</t>
+          <t>3170.808</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2010,562 +2010,562 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>161.0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-2.88</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>-0.73</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>37.33333333333334</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2026-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>弱勢</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>弱勢</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>18.8</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>C2 循環・中段</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>中段</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>業外占比&gt;50% / 毛利率連2季低於8季均</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>-852182.0</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.29</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>2026-09-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>5.98</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>192.0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>152.5</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>3171</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>18.63</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>0.81</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>-3.95</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>-4.52</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>-5.12</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>166.28</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>174.15</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>0.001253918495297768</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>-0.002171889543903127</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>-0.002250225022502272</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>-7.75</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>-4.18</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>-3.88</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>2026/09/30</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>1563422357.758197</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>509244108.0</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>234539382.2</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>253188397.8</t>
+        </is>
+      </c>
+      <c r="CK3" t="inlineStr">
+        <is>
+          <t>343595526.6</t>
+        </is>
+      </c>
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>792942420.6</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>-48482412.48764507</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
+          <t>2026/07/03</t>
+        </is>
+      </c>
+      <c r="CP3" t="inlineStr">
+        <is>
+          <t>-21.27</t>
+        </is>
+      </c>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>雷虎</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>雷虎</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="CT3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="CU3" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="CV3" t="inlineStr">
+        <is>
+          <t>-33.24457817645055</t>
+        </is>
+      </c>
+      <c r="CW3" t="inlineStr">
+        <is>
+          <t>27.91049322280965</t>
+        </is>
+      </c>
+      <c r="CX3" t="inlineStr">
+        <is>
+          <t>14.8350157059527</t>
+        </is>
+      </c>
+      <c r="CY3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CZ3" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="DA3" t="inlineStr">
+        <is>
+          <t>8.14</t>
+        </is>
+      </c>
+      <c r="DB3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DC3" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="DD3" t="inlineStr">
+        <is>
+          <t>335.42</t>
+        </is>
+      </c>
+      <c r="DE3" t="inlineStr">
+        <is>
+          <t>35.54</t>
+        </is>
+      </c>
+      <c r="DF3" t="inlineStr">
+        <is>
+          <t>0.10</t>
+        </is>
+      </c>
+      <c r="DG3" t="inlineStr">
+        <is>
+          <t>71.41</t>
+        </is>
+      </c>
+      <c r="DH3" t="inlineStr">
+        <is>
+          <t>26505</t>
+        </is>
+      </c>
+      <c r="DI3" t="inlineStr">
+        <is>
+          <t>無人載具暨模型產品51.59%、口腔醫療器材25.92%、無菌包材18.42%、其他2.98%、鋁船1.08% (2025年)</t>
+        </is>
+      </c>
+      <c r="DJ3" t="inlineStr">
+        <is>
+          <t>雷虎-其他-上市</t>
+        </is>
+      </c>
+      <c r="DK3" t="inlineStr">
+        <is>
+          <t>其他右上上市</t>
+        </is>
+      </c>
+      <c r="DL3" t="inlineStr">
+        <is>
+          <t>163.0</t>
+        </is>
+      </c>
+      <c r="DM3" t="inlineStr">
+        <is>
+          <t>163.0</t>
+        </is>
+      </c>
+      <c r="DN3" t="inlineStr">
+        <is>
           <t>158.5</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>-1.81</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>34.66666666666666</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>2026-08-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>弱勢</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>弱勢</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>18.8</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>C2 循環・中段</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>中段</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>35.0</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>業外占比&gt;50% / 毛利率連2季低於8季均</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>-127183.0</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>2026-09-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>-1.25</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>152.5</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>1022</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>5.88</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>-0.63</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>-4.29</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>-4.55</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>-5.03</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>166.65</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>174.6</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>-0.003125000000000044</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>-0.005860579888957385</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>-0.002991325157044589</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>-15.46</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>-4.39</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>-3.80</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>2026/09/30</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>1565861150.593151</t>
-        </is>
-      </c>
-      <c r="CH3" t="inlineStr">
-        <is>
-          <t>161638060.0</t>
-        </is>
-      </c>
-      <c r="CI3" t="inlineStr">
-        <is>
-          <t>180376169.4</t>
-        </is>
-      </c>
-      <c r="CJ3" t="inlineStr">
-        <is>
-          <t>240845440.2</t>
-        </is>
-      </c>
-      <c r="CK3" t="inlineStr">
-        <is>
-          <t>336505518.2333333</t>
-        </is>
-      </c>
-      <c r="CL3" t="inlineStr">
-        <is>
-          <t>816667243.86</t>
-        </is>
-      </c>
-      <c r="CM3" t="inlineStr">
-        <is>
-          <t>-54162405.88001794</t>
-        </is>
-      </c>
-      <c r="CN3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CO3" t="inlineStr">
-        <is>
-          <t>2026/07/03</t>
-        </is>
-      </c>
-      <c r="CP3" t="inlineStr">
-        <is>
-          <t>-22.49</t>
-        </is>
-      </c>
-      <c r="CQ3" t="inlineStr">
-        <is>
-          <t>雷虎</t>
-        </is>
-      </c>
-      <c r="CR3" t="inlineStr">
-        <is>
-          <t>雷虎</t>
-        </is>
-      </c>
-      <c r="CS3" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="CT3" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="CU3" t="inlineStr">
-        <is>
-          <t>0.86</t>
-        </is>
-      </c>
-      <c r="CV3" t="inlineStr">
-        <is>
-          <t>-33.24457817645055</t>
-        </is>
-      </c>
-      <c r="CW3" t="inlineStr">
-        <is>
-          <t>27.91049322280965</t>
-        </is>
-      </c>
-      <c r="CX3" t="inlineStr">
-        <is>
-          <t>14.8350157059527</t>
-        </is>
-      </c>
-      <c r="CY3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CZ3" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="DA3" t="inlineStr">
-        <is>
-          <t>8.02</t>
-        </is>
-      </c>
-      <c r="DB3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DC3" t="inlineStr">
-        <is>
-          <t>2.82</t>
-        </is>
-      </c>
-      <c r="DD3" t="inlineStr">
-        <is>
-          <t>330.21</t>
-        </is>
-      </c>
-      <c r="DE3" t="inlineStr">
-        <is>
-          <t>35.54</t>
-        </is>
-      </c>
-      <c r="DF3" t="inlineStr">
-        <is>
-          <t>0.10</t>
-        </is>
-      </c>
-      <c r="DG3" t="inlineStr">
-        <is>
-          <t>72.46</t>
-        </is>
-      </c>
-      <c r="DH3" t="inlineStr">
-        <is>
-          <t>26094</t>
-        </is>
-      </c>
-      <c r="DI3" t="inlineStr">
-        <is>
-          <t>無人載具暨模型產品51.59%、口腔醫療器材25.92%、無菌包材18.42%、其他2.98%、鋁船1.08% (2025年)</t>
-        </is>
-      </c>
-      <c r="DJ3" t="inlineStr">
-        <is>
-          <t>雷虎-其他-上市</t>
-        </is>
-      </c>
-      <c r="DK3" t="inlineStr">
-        <is>
-          <t>其他右上上市</t>
-        </is>
-      </c>
-      <c r="DL3" t="inlineStr">
+      <c r="DO3" t="inlineStr">
         <is>
           <t>161.0</t>
-        </is>
-      </c>
-      <c r="DM3" t="inlineStr">
-        <is>
-          <t>162.5</t>
-        </is>
-      </c>
-      <c r="DN3" t="inlineStr">
-        <is>
-          <t>156.5</t>
-        </is>
-      </c>
-      <c r="DO3" t="inlineStr">
-        <is>
-          <t>158.5</t>
         </is>
       </c>
       <c r="DP3" t="inlineStr">
@@ -2767,12 +2767,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1007.021</t>
+          <t>1021.557</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>158.5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -2792,17 +2792,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>34.66666666666666</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>230112.0</t>
+          <t>-127183.0</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -2992,17 +2992,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -3082,82 +3082,82 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.55</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-5.03</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>167.15</t>
+          <t>166.65</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>174.89</t>
+          <t>174.6</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>-0.007444168734491274</t>
+          <t>-0.003125000000000044</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>-0.007652280379553122</t>
+          <t>-0.005860579888957385</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>-0.003428230734833781</t>
+          <t>-0.002991325157044589</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>-18.80</t>
+          <t>-15.46</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-3.80</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -3167,37 +3167,37 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>1565861150.593151</t>
+          <t>1563422357.758197</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>160209039.0</t>
+          <t>161638060.0</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>203692745.0</t>
+          <t>180376169.4</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>252419462.8</t>
+          <t>240845440.2</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>339159286.6</t>
+          <t>336505518.2333333</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>860809858.3</t>
+          <t>816667243.86</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>-55874212.41063066</t>
+          <t>-54162405.88001794</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>-22.74</t>
+          <t>-22.49</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="CU4" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="CV4" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="DA4" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="DB4" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="DD4" t="inlineStr">
         <is>
-          <t>330.21</t>
+          <t>335.42</t>
         </is>
       </c>
       <c r="DE4" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="DG4" t="inlineStr">
         <is>
-          <t>72.46</t>
+          <t>71.41</t>
         </is>
       </c>
       <c r="DH4" t="inlineStr">
         <is>
-          <t>26094</t>
+          <t>26505</t>
         </is>
       </c>
       <c r="DI4" t="inlineStr">
@@ -3322,22 +3322,22 @@
       </c>
       <c r="DL4" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="DM4" t="inlineStr">
         <is>
-          <t>161.5</t>
+          <t>162.5</t>
         </is>
       </c>
       <c r="DN4" t="inlineStr">
         <is>
-          <t>157.0</t>
+          <t>156.5</t>
         </is>
       </c>
       <c r="DO4" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>158.5</t>
         </is>
       </c>
       <c r="DP4" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1133.854</t>
+          <t>1007.021</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3564,17 +3564,17 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>29.33333333333333</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>57008.0</t>
+          <t>230112.0</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -3764,17 +3764,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>-4.11</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -3869,67 +3869,67 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>-4.44</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>167.72</t>
+          <t>167.15</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>175.51</t>
+          <t>174.89</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.007444168734491274</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>-0.009699909063352496</t>
+          <t>-0.007652280379553122</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>-0.00386043058648855</t>
+          <t>-0.003428230734833781</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>-19.63</t>
+          <t>-18.80</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -3939,37 +3939,37 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>1565861150.593151</t>
+          <t>1563422357.758197</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>181915550.0</t>
+          <t>160209039.0</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>218690414.6</t>
+          <t>203692745.0</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>261760977.3</t>
+          <t>252419462.8</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>345980918.2</t>
+          <t>339159286.6</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>888453396.8</t>
+          <t>860809858.3</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>-57815209.5356372</t>
+          <t>-55874212.41063066</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="CU5" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="CV5" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CZ5" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="DD5" t="inlineStr">
         <is>
-          <t>330.21</t>
+          <t>335.42</t>
         </is>
       </c>
       <c r="DE5" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="DG5" t="inlineStr">
         <is>
-          <t>72.46</t>
+          <t>71.41</t>
         </is>
       </c>
       <c r="DH5" t="inlineStr">
         <is>
-          <t>26094</t>
+          <t>26505</t>
         </is>
       </c>
       <c r="DI5" t="inlineStr">
@@ -4094,17 +4094,17 @@
       </c>
       <c r="DL5" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="DM5" t="inlineStr">
         <is>
-          <t>164.5</t>
+          <t>161.5</t>
         </is>
       </c>
       <c r="DN5" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>157.0</t>
         </is>
       </c>
       <c r="DO5" t="inlineStr">
@@ -4311,12 +4311,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>981.651</t>
+          <t>1133.854</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -4336,17 +4336,17 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>26.66666666666667</t>
+          <t>29.33333333333333</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4391,12 +4391,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>333762.0</t>
+          <t>57008.0</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -4536,17 +4536,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-4.11</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -4626,82 +4626,82 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-4.44</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>168.38</t>
+          <t>167.72</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>175.79</t>
+          <t>175.51</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>-0.004323656578134716</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>-0.006325301204819334</t>
+          <t>-0.009699909063352496</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>-0.00281314776428776</t>
+          <t>-0.00386043058648855</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>-17.24</t>
+          <t>-19.63</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -4711,37 +4711,37 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>1565861150.593151</t>
+          <t>1563422357.758197</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>159690154.0</t>
+          <t>181915550.0</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>267724697.4</t>
+          <t>218690414.6</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>290869867.4</t>
+          <t>261760977.3</t>
         </is>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>353763755.5</t>
+          <t>345980918.2</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>907379890.2</t>
+          <t>888453396.8</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>-60313241.59743214</t>
+          <t>-57815209.5356372</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>-20.29</t>
+          <t>-22.74</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="CU6" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="CV6" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="CY6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CZ6" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="DA6" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="DB6" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="DD6" t="inlineStr">
         <is>
-          <t>330.21</t>
+          <t>335.42</t>
         </is>
       </c>
       <c r="DE6" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="DG6" t="inlineStr">
         <is>
-          <t>72.46</t>
+          <t>71.41</t>
         </is>
       </c>
       <c r="DH6" t="inlineStr">
         <is>
-          <t>26094</t>
+          <t>26505</t>
         </is>
       </c>
       <c r="DI6" t="inlineStr">
@@ -4866,22 +4866,22 @@
       </c>
       <c r="DL6" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="DM6" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>164.5</t>
         </is>
       </c>
       <c r="DN6" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="DO6" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="DP6" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1469.66</t>
+          <t>981.651</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -5108,17 +5108,17 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>26.66666666666667</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2807.0</t>
+          <t>333762.0</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -5308,17 +5308,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -5398,82 +5398,82 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>22.92</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>168.85</t>
+          <t>168.38</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>176.23</t>
+          <t>175.79</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>-0.005528255528255532</t>
+          <t>-0.004323656578134716</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>-0.007770472205618661</t>
+          <t>-0.006325301204819334</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>-0.002363367799113725</t>
+          <t>-0.00281314776428776</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>-25.37</t>
+          <t>-17.24</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -5483,37 +5483,37 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>1565861150.593151</t>
+          <t>1563422357.758197</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>238428044.0</t>
+          <t>159690154.0</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>271837413.4</t>
+          <t>267724697.4</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>302992813.7</t>
+          <t>290869867.4</t>
         </is>
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>365181454.0666667</t>
+          <t>353763755.5</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>906416201.24</t>
+          <t>907379890.2</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>-63420424.30220893</t>
+          <t>-60313241.59743214</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>-21.76</t>
+          <t>-20.29</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="CU7" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="CV7" t="inlineStr">
@@ -5573,17 +5573,17 @@
       </c>
       <c r="CY7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="DA7" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="DB7" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="DD7" t="inlineStr">
         <is>
-          <t>330.21</t>
+          <t>335.42</t>
         </is>
       </c>
       <c r="DE7" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="DG7" t="inlineStr">
         <is>
-          <t>72.46</t>
+          <t>71.41</t>
         </is>
       </c>
       <c r="DH7" t="inlineStr">
         <is>
-          <t>26094</t>
+          <t>26505</t>
         </is>
       </c>
       <c r="DI7" t="inlineStr">
@@ -5638,22 +5638,22 @@
       </c>
       <c r="DL7" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="DM7" t="inlineStr">
         <is>
-          <t>165.5</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="DN7" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="DO7" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="DP7" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1750.181</t>
+          <t>1469.66</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -5880,17 +5880,17 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>21.33333333333333</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>-305385.0</t>
+          <t>2807.0</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -6080,17 +6080,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -6170,82 +6170,82 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>169.25</t>
+          <t>168.85</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>176.83</t>
+          <t>176.23</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>-0.008526187576126554</t>
+          <t>-0.005528255528255532</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>-0.008298755186721851</t>
+          <t>-0.007770472205618661</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>-0.002357795461243817</t>
+          <t>-0.002363367799113725</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>-25.50</t>
+          <t>-25.37</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -6255,37 +6255,37 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>1565861150.593151</t>
+          <t>1563422357.758197</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>278220938.0</t>
+          <t>238428044.0</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>301314711.0</t>
+          <t>271837413.4</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>313608656.4</t>
+          <t>302992813.7</t>
         </is>
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>389740534.1</t>
+          <t>365181454.0666667</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>904762468.58</t>
+          <t>906416201.24</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>-68027560.89944758</t>
+          <t>-63420424.30220893</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>-21.27</t>
+          <t>-21.76</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="CU8" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="CV8" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="CY8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CZ8" t="inlineStr">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="DA8" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="DB8" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="DD8" t="inlineStr">
         <is>
-          <t>330.21</t>
+          <t>335.42</t>
         </is>
       </c>
       <c r="DE8" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="DG8" t="inlineStr">
         <is>
-          <t>72.46</t>
+          <t>71.41</t>
         </is>
       </c>
       <c r="DH8" t="inlineStr">
         <is>
-          <t>26094</t>
+          <t>26505</t>
         </is>
       </c>
       <c r="DI8" t="inlineStr">
@@ -6415,17 +6415,17 @@
       </c>
       <c r="DM8" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>165.5</t>
         </is>
       </c>
       <c r="DN8" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="DO8" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="DP8" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1432.306</t>
+          <t>1750.181</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -6652,17 +6652,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>18.66666666666667</t>
+          <t>21.33333333333333</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -6707,12 +6707,12 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>352116.0</t>
+          <t>-305385.0</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -6852,17 +6852,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -6942,82 +6942,82 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>-4.36</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>169.65</t>
+          <t>169.25</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>177.39</t>
+          <t>176.83</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>-0.007854984894259842</t>
+          <t>-0.008526187576126554</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>-0.006770680011775165</t>
+          <t>-0.008298755186721851</t>
         </is>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>-0.0007362685907819078</t>
+          <t>-0.002357795461243817</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>-24.36</t>
+          <t>-25.50</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -7027,37 +7027,37 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>1565861150.593151</t>
+          <t>1563422357.758197</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>235197387.0</t>
+          <t>278220938.0</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>301146180.6</t>
+          <t>301314711.0</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>317773316.9</t>
+          <t>313608656.4</t>
         </is>
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>406754825.0666667</t>
+          <t>389740534.1</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>903253218.24</t>
+          <t>904762468.58</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>-73521514.87259929</t>
+          <t>-68027560.89944758</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>-19.80</t>
+          <t>-21.27</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="CU9" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="CV9" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="CY9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CZ9" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="DA9" t="inlineStr">
         <is>
-          <t>8.30</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="DB9" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="DD9" t="inlineStr">
         <is>
-          <t>330.21</t>
+          <t>335.42</t>
         </is>
       </c>
       <c r="DE9" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="DG9" t="inlineStr">
         <is>
-          <t>72.46</t>
+          <t>71.41</t>
         </is>
       </c>
       <c r="DH9" t="inlineStr">
         <is>
-          <t>26094</t>
+          <t>26505</t>
         </is>
       </c>
       <c r="DI9" t="inlineStr">
@@ -7182,22 +7182,22 @@
       </c>
       <c r="DL9" t="inlineStr">
         <is>
-          <t>160.5</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="DM9" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="DN9" t="inlineStr">
         <is>
-          <t>160.5</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="DO9" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="DP9" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-5.17</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2658.429</t>
+          <t>1432.306</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -7424,17 +7424,17 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>18.66666666666667</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>16582.0</t>
+          <t>352116.0</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -7624,17 +7624,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -7714,82 +7714,82 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>46</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>18.56</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>-4.36</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>169.78</t>
+          <t>169.65</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>177.68</t>
+          <t>177.39</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>-0.01896858328393591</t>
+          <t>-0.007854984894259842</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
         <is>
-          <t>-0.009620991253644351</t>
+          <t>-0.006770680011775165</t>
         </is>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>-0.004690019053202321</t>
+          <t>-0.0007362685907819078</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>-29.06</t>
+          <t>-24.36</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -7799,37 +7799,37 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>1565861150.593151</t>
+          <t>1563422357.758197</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>427086964.0</t>
+          <t>235197387.0</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>304831540.0</t>
+          <t>301146180.6</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>324241749.9</t>
+          <t>317773316.9</t>
         </is>
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>420129618.6666667</t>
+          <t>406754825.0666667</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>901722629.6</t>
+          <t>903253218.24</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>-79554931.19709314</t>
+          <t>-73521514.87259929</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>-22.74</t>
+          <t>-19.80</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="CU10" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="CV10" t="inlineStr">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="CY10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CZ10" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="DA10" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="DB10" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="DD10" t="inlineStr">
         <is>
-          <t>330.21</t>
+          <t>335.42</t>
         </is>
       </c>
       <c r="DE10" t="inlineStr">
@@ -7929,12 +7929,12 @@
       </c>
       <c r="DG10" t="inlineStr">
         <is>
-          <t>72.46</t>
+          <t>71.41</t>
         </is>
       </c>
       <c r="DH10" t="inlineStr">
         <is>
-          <t>26094</t>
+          <t>26505</t>
         </is>
       </c>
       <c r="DI10" t="inlineStr">
@@ -7954,22 +7954,22 @@
       </c>
       <c r="DL10" t="inlineStr">
         <is>
-          <t>164.5</t>
+          <t>160.5</t>
         </is>
       </c>
       <c r="DM10" t="inlineStr">
         <is>
-          <t>165.5</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="DN10" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>160.5</t>
         </is>
       </c>
       <c r="DO10" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="DP10" t="inlineStr">
@@ -8171,12 +8171,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>4732.186</t>
+          <t>5054.622</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -8201,12 +8201,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -8381,12 +8381,12 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>-155349.0</t>
+          <t>1665784.0</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
@@ -8396,17 +8396,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -8486,12 +8486,12 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>51</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>4949</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -8501,67 +8501,67 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>22.92</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>62.42</t>
+          <t>62.2</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>64.85</t>
+          <t>64.61</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>-0.003275466754012468</t>
+          <t>-0.009201445941505182</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
         <is>
-          <t>-0.002284595300261039</t>
+          <t>-0.00523388943408587</t>
         </is>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>-0.002477225507431791</t>
+          <t>-0.003364575823119442</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>-16.33</t>
+          <t>-23.33</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -8571,37 +8571,37 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>1664151582.530137</t>
+          <t>1660823897.512295</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>285457373.0</t>
+          <t>297479244.0</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>255815197.2</t>
+          <t>265024171.4</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>272331780.9</t>
+          <t>279629731.8</t>
         </is>
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>392725763.9666666</t>
+          <t>365782755.2</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>1459362947.68</t>
+          <t>1356677219.66</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>-86503755.69802816</t>
+          <t>-79349401.72229505</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>13.27</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="CY11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CZ11" t="inlineStr">
@@ -8671,12 +8671,12 @@
       </c>
       <c r="DA11" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="DB11" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="DC11" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="DD11" t="inlineStr">
         <is>
-          <t>29.42</t>
+          <t>28.99</t>
         </is>
       </c>
       <c r="DE11" t="inlineStr">
@@ -8701,12 +8701,12 @@
       </c>
       <c r="DG11" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>22.17</t>
         </is>
       </c>
       <c r="DH11" t="inlineStr">
         <is>
-          <t>57360</t>
+          <t>56512</t>
         </is>
       </c>
       <c r="DI11" t="inlineStr">
@@ -8726,22 +8726,22 @@
       </c>
       <c r="DL11" t="inlineStr">
         <is>
-          <t>61.5</t>
+          <t>59.6</t>
         </is>
       </c>
       <c r="DM11" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>59.7</t>
         </is>
       </c>
       <c r="DN11" t="inlineStr">
         <is>
-          <t>59.9</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="DO11" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="DP11" t="inlineStr">
@@ -8943,12 +8943,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>4948.586</t>
+          <t>4732.186</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -8968,17 +8968,17 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1.333333333333333</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -9153,12 +9153,12 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>-1273743.0</t>
+          <t>-155349.0</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
@@ -9168,17 +9168,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -9258,17 +9258,17 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>51</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>4949</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -9278,62 +9278,62 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>62.57</t>
+          <t>62.42</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>64.93</t>
+          <t>64.85</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>-0.0009816753926702448</t>
+          <t>-0.003275466754012468</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>-0.002604166666666741</t>
+          <t>-0.002284595300261039</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>-0.001276935355147502</t>
+          <t>-0.002477225507431791</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>-13.63</t>
+          <t>-16.33</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -9343,37 +9343,37 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>1664151582.530137</t>
+          <t>1660823897.512295</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>301938297.0</t>
+          <t>285457373.0</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>244686220.0</t>
+          <t>255815197.2</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>287329181.0</t>
+          <t>272331780.9</t>
         </is>
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>402223738.6</t>
+          <t>392725763.9666666</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>1494487563.94</t>
+          <t>1459362947.68</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>-93672714.03781335</t>
+          <t>-86503755.69802816</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -9388,7 +9388,7 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="CY12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CZ12" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="DA12" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="DB12" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="DC12" t="inlineStr">
@@ -9458,7 +9458,7 @@
       </c>
       <c r="DD12" t="inlineStr">
         <is>
-          <t>29.42</t>
+          <t>28.99</t>
         </is>
       </c>
       <c r="DE12" t="inlineStr">
@@ -9473,12 +9473,12 @@
       </c>
       <c r="DG12" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>22.17</t>
         </is>
       </c>
       <c r="DH12" t="inlineStr">
         <is>
-          <t>57360</t>
+          <t>56512</t>
         </is>
       </c>
       <c r="DI12" t="inlineStr">
@@ -9498,22 +9498,22 @@
       </c>
       <c r="DL12" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>61.5</t>
         </is>
       </c>
       <c r="DM12" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="DN12" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>59.9</t>
         </is>
       </c>
       <c r="DO12" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="DP12" t="inlineStr">
@@ -9715,12 +9715,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>3650.736</t>
+          <t>4948.586</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -9730,7 +9730,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -9740,17 +9740,17 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -9850,7 +9850,7 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -9925,12 +9925,12 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>1617243.0</t>
+          <t>-1273743.0</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
@@ -9940,17 +9940,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -10030,82 +10030,82 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>51</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>4949</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>27.92</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>62.65</t>
+          <t>62.57</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>64.95</t>
+          <t>64.93</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>-0.00293637846655781</t>
+          <t>-0.0009816753926702448</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
         <is>
-          <t>-0.003244646333549706</t>
+          <t>-0.002604166666666741</t>
         </is>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>-0.00151406486572625</t>
+          <t>-0.001276935355147502</t>
         </is>
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>-17.31</t>
+          <t>-13.63</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
@@ -10115,37 +10115,37 @@
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>1664151582.530137</t>
+          <t>1660823897.512295</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
         <is>
-          <t>223133727.0</t>
+          <t>301938297.0</t>
         </is>
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>236126131.4</t>
+          <t>244686220.0</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
         <is>
-          <t>287593006.0</t>
+          <t>287329181.0</t>
         </is>
       </c>
       <c r="CK13" t="inlineStr">
         <is>
-          <t>408439857.3333333</t>
+          <t>402223738.6</t>
         </is>
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>1504692590.78</t>
+          <t>1494487563.94</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>-100847579.7308799</t>
+          <t>-93672714.03781335</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -10160,7 +10160,7 @@
       </c>
       <c r="CP13" t="inlineStr">
         <is>
-          <t>17.69</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="CQ13" t="inlineStr">
@@ -10205,7 +10205,7 @@
       </c>
       <c r="CY13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CZ13" t="inlineStr">
@@ -10215,12 +10215,12 @@
       </c>
       <c r="DA13" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="DB13" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="DC13" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="DD13" t="inlineStr">
         <is>
-          <t>29.42</t>
+          <t>28.99</t>
         </is>
       </c>
       <c r="DE13" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="DG13" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>22.17</t>
         </is>
       </c>
       <c r="DH13" t="inlineStr">
         <is>
-          <t>57360</t>
+          <t>56512</t>
         </is>
       </c>
       <c r="DI13" t="inlineStr">
@@ -10275,17 +10275,17 @@
       </c>
       <c r="DM13" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>61.7</t>
         </is>
       </c>
       <c r="DN13" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="DO13" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="DP13" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>3554.399</t>
+          <t>3650.736</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -10502,7 +10502,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -10512,17 +10512,17 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -10567,64 +10567,64 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
       <c r="AG14" t="inlineStr">
         <is>
           <t>弱勢</t>
@@ -10697,12 +10697,12 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>561677.0</t>
+          <t>1617243.0</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
@@ -10712,17 +10712,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -10802,82 +10802,82 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>51</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>4949</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>27.92</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>62.74</t>
+          <t>62.65</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>64.98</t>
+          <t>64.95</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>-0.0006521030322791388</t>
+          <t>-0.00293637846655781</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
         <is>
-          <t>-0.005004035512510163</t>
+          <t>-0.003244646333549706</t>
         </is>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>-0.002543518003338407</t>
+          <t>-0.00151406486572625</t>
         </is>
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>-24.40</t>
+          <t>-17.31</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
@@ -10887,37 +10887,37 @@
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>1664151582.530137</t>
+          <t>1660823897.512295</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
         <is>
-          <t>217112216.0</t>
+          <t>223133727.0</t>
         </is>
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>257978567.8</t>
+          <t>236126131.4</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
         <is>
-          <t>289865296.4</t>
+          <t>287593006.0</t>
         </is>
       </c>
       <c r="CK14" t="inlineStr">
         <is>
-          <t>445589655.3666667</t>
+          <t>408439857.3333333</t>
         </is>
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>1539054093.44</t>
+          <t>1504692590.78</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>-107504300.6464289</t>
+          <t>-100847579.7308799</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -10932,7 +10932,7 @@
       </c>
       <c r="CP14" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>17.69</t>
         </is>
       </c>
       <c r="CQ14" t="inlineStr">
@@ -10977,7 +10977,7 @@
       </c>
       <c r="CY14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CZ14" t="inlineStr">
@@ -10987,12 +10987,12 @@
       </c>
       <c r="DA14" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="DB14" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="DC14" t="inlineStr">
@@ -11002,7 +11002,7 @@
       </c>
       <c r="DD14" t="inlineStr">
         <is>
-          <t>29.42</t>
+          <t>28.99</t>
         </is>
       </c>
       <c r="DE14" t="inlineStr">
@@ -11017,12 +11017,12 @@
       </c>
       <c r="DG14" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>22.17</t>
         </is>
       </c>
       <c r="DH14" t="inlineStr">
         <is>
-          <t>57360</t>
+          <t>56512</t>
         </is>
       </c>
       <c r="DI14" t="inlineStr">
@@ -11042,22 +11042,22 @@
       </c>
       <c r="DL14" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="DM14" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="DN14" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="DO14" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="DP14" t="inlineStr">
@@ -11259,12 +11259,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>4081.521</t>
+          <t>3554.399</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -11284,199 +11284,199 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1.333333333333333</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>2026-08-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>弱勢</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>弱勢</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>B1 成長股</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>561677.0</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
           <t>-0.02</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>1.333333333333333</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>2026-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>弱勢</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>弱勢</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>B1 成長股</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>98.0</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>1122710.0</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
       <c r="AW15" t="inlineStr">
         <is>
           <t>2026-08-21 00:00:00</t>
@@ -11484,17 +11484,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -11574,82 +11574,82 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>51</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>4949</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>62.9</t>
+          <t>62.74</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>64.99</t>
+          <t>64.98</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>-0.001302507326603752</t>
+          <t>-0.0006521030322791388</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
         <is>
-          <t>-0.003859141341051808</t>
+          <t>-0.005004035512510163</t>
         </is>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>-0.002299762093576629</t>
+          <t>-0.002543518003338407</t>
         </is>
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>-23.02</t>
+          <t>-24.40</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
@@ -11659,37 +11659,37 @@
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>1664151582.530137</t>
+          <t>1660823897.512295</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
         <is>
-          <t>251434373.0</t>
+          <t>217112216.0</t>
         </is>
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>294235292.2</t>
+          <t>257978567.8</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
         <is>
-          <t>298762155.6</t>
+          <t>289865296.4</t>
         </is>
       </c>
       <c r="CK15" t="inlineStr">
         <is>
-          <t>462107574.7</t>
+          <t>445589655.3666667</t>
         </is>
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>1549379054.62</t>
+          <t>1539054093.44</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>-114719794.4941481</t>
+          <t>-107504300.6464289</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="CP15" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="CQ15" t="inlineStr">
@@ -11759,12 +11759,12 @@
       </c>
       <c r="DA15" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="DB15" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="DC15" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="DD15" t="inlineStr">
         <is>
-          <t>29.42</t>
+          <t>28.99</t>
         </is>
       </c>
       <c r="DE15" t="inlineStr">
@@ -11789,12 +11789,12 @@
       </c>
       <c r="DG15" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>22.17</t>
         </is>
       </c>
       <c r="DH15" t="inlineStr">
         <is>
-          <t>57360</t>
+          <t>56512</t>
         </is>
       </c>
       <c r="DI15" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="DL15" t="inlineStr">
         <is>
-          <t>61.5</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="DM15" t="inlineStr">
@@ -11824,12 +11824,12 @@
       </c>
       <c r="DN15" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="DO15" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="DP15" t="inlineStr">
@@ -12031,12 +12031,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>3737.149</t>
+          <t>4081.521</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -12046,7 +12046,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>61.7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -12056,17 +12056,17 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-4.75</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -12241,12 +12241,12 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>1159645.0</t>
+          <t>1122710.0</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
@@ -12256,17 +12256,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -12346,47 +12346,47 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>51</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>4949</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>20.32</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>63.05</t>
+          <t>62.9</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
@@ -12396,32 +12396,32 @@
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>-0.001300813008130008</t>
+          <t>-0.001302507326603752</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
         <is>
-          <t>-0.005755395683452957</t>
+          <t>-0.003859141341051808</t>
         </is>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>-0.002294485323206086</t>
+          <t>-0.002299762093576629</t>
         </is>
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>-33.94</t>
+          <t>-23.02</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
@@ -12431,37 +12431,37 @@
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>1664151582.530137</t>
+          <t>1660823897.512295</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
         <is>
-          <t>229812487.0</t>
+          <t>251434373.0</t>
         </is>
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>288848364.6</t>
+          <t>294235292.2</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
         <is>
-          <t>306794601.5</t>
+          <t>298762155.6</t>
         </is>
       </c>
       <c r="CK16" t="inlineStr">
         <is>
-          <t>474975135.4333333</t>
+          <t>462107574.7</t>
         </is>
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>1561341037.2</t>
+          <t>1549379054.62</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>-122874110.7683322</t>
+          <t>-114719794.4941481</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -12476,7 +12476,7 @@
       </c>
       <c r="CP16" t="inlineStr">
         <is>
-          <t>17.31</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="CQ16" t="inlineStr">
@@ -12531,12 +12531,12 @@
       </c>
       <c r="DA16" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="DB16" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="DC16" t="inlineStr">
@@ -12546,7 +12546,7 @@
       </c>
       <c r="DD16" t="inlineStr">
         <is>
-          <t>29.42</t>
+          <t>28.99</t>
         </is>
       </c>
       <c r="DE16" t="inlineStr">
@@ -12561,12 +12561,12 @@
       </c>
       <c r="DG16" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>22.17</t>
         </is>
       </c>
       <c r="DH16" t="inlineStr">
         <is>
-          <t>57360</t>
+          <t>56512</t>
         </is>
       </c>
       <c r="DI16" t="inlineStr">
@@ -12586,22 +12586,22 @@
       </c>
       <c r="DL16" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>61.5</t>
         </is>
       </c>
       <c r="DM16" t="inlineStr">
         <is>
-          <t>62.3</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="DN16" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>61.1</t>
         </is>
       </c>
       <c r="DO16" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>61.7</t>
         </is>
       </c>
       <c r="DP16" t="inlineStr">
@@ -12803,244 +12803,244 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>3737.149</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>61.0</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-3.57</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1.333333333333333</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>2026-08-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>弱勢</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>弱勢</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>B1 成長股</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>1159645.0</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>2026-08-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
           <t>-1.47</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>4255.697</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>61.2</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>-1.06</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>1.333333333333333</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>2026-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>弱勢</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>B1 成長股</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>98.0</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>-58553.0</t>
-        </is>
-      </c>
-      <c r="AV17" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>2026-08-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>2.77</t>
-        </is>
-      </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
       <c r="BA17" t="inlineStr">
         <is>
           <t>False</t>
@@ -13118,82 +13118,82 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>51</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>4949</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>20.32</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>63.05</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>65.01</t>
+          <t>64.99</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>-0.004209844559585618</t>
+          <t>-0.001300813008130008</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
         <is>
-          <t>-0.007615421227986641</t>
+          <t>-0.005755395683452957</t>
         </is>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>-0.002997554626488874</t>
+          <t>-0.002294485323206086</t>
         </is>
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>-37.43</t>
+          <t>-33.94</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
@@ -13203,37 +13203,37 @@
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>1664151582.530137</t>
+          <t>1660823897.512295</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
         <is>
-          <t>259137854.0</t>
+          <t>229812487.0</t>
         </is>
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>329972142.0</t>
+          <t>288848364.6</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
         <is>
-          <t>351121915.2</t>
+          <t>306794601.5</t>
         </is>
       </c>
       <c r="CK17" t="inlineStr">
         <is>
-          <t>501047004.2333333</t>
+          <t>474975135.4333333</t>
         </is>
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>1579196558.12</t>
+          <t>1561341037.2</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>-131763145.3514566</t>
+          <t>-122874110.7683322</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="CP17" t="inlineStr">
         <is>
-          <t>17.69</t>
+          <t>17.31</t>
         </is>
       </c>
       <c r="CQ17" t="inlineStr">
@@ -13293,7 +13293,7 @@
       </c>
       <c r="CY17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CZ17" t="inlineStr">
@@ -13303,12 +13303,12 @@
       </c>
       <c r="DA17" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="DB17" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="DC17" t="inlineStr">
@@ -13318,7 +13318,7 @@
       </c>
       <c r="DD17" t="inlineStr">
         <is>
-          <t>29.42</t>
+          <t>28.99</t>
         </is>
       </c>
       <c r="DE17" t="inlineStr">
@@ -13333,12 +13333,12 @@
       </c>
       <c r="DG17" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>22.17</t>
         </is>
       </c>
       <c r="DH17" t="inlineStr">
         <is>
-          <t>57360</t>
+          <t>56512</t>
         </is>
       </c>
       <c r="DI17" t="inlineStr">
@@ -13358,22 +13358,22 @@
       </c>
       <c r="DL17" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="DM17" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>62.3</t>
         </is>
       </c>
       <c r="DN17" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="DO17" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="DP17" t="inlineStr">
@@ -13575,12 +13575,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>5366.395</t>
+          <t>4255.697</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -13590,7 +13590,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>62.1</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -13600,17 +13600,17 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -13655,12 +13655,12 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -13710,19 +13710,19 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
+          <t>弱勢</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
           <t>盤整</t>
         </is>
       </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>弱勢</t>
-        </is>
-      </c>
       <c r="AI18" t="inlineStr">
         <is>
           <t>75.0</t>
@@ -13785,12 +13785,12 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>3063402.0</t>
+          <t>-58553.0</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
@@ -13800,17 +13800,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -13890,82 +13890,82 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>51</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>4949</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>35.9</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>16.87</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>63.39</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>65.06</t>
+          <t>65.01</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>-0.00354953210713127</t>
+          <t>-0.004209844559585618</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
         <is>
-          <t>-0.003635788808093565</t>
+          <t>-0.007615421227986641</t>
         </is>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>7.888923950782889e-05</t>
+          <t>-0.002997554626488874</t>
         </is>
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>-40.48</t>
+          <t>-37.43</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
@@ -13975,37 +13975,37 @@
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>1664151582.530137</t>
+          <t>1660823897.512295</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
         <is>
-          <t>332395909.0</t>
+          <t>259137854.0</t>
         </is>
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>339059880.6</t>
+          <t>329972142.0</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
         <is>
-          <t>409533935.4</t>
+          <t>351121915.2</t>
         </is>
       </c>
       <c r="CK18" t="inlineStr">
         <is>
-          <t>517834921.1666667</t>
+          <t>501047004.2333333</t>
         </is>
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>1623092805.68</t>
+          <t>1579196558.12</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>-142101585.2845038</t>
+          <t>-131763145.3514566</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -14020,7 +14020,7 @@
       </c>
       <c r="CP18" t="inlineStr">
         <is>
-          <t>19.42</t>
+          <t>17.69</t>
         </is>
       </c>
       <c r="CQ18" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="CY18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CZ18" t="inlineStr">
@@ -14075,12 +14075,12 @@
       </c>
       <c r="DA18" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="DB18" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="DC18" t="inlineStr">
@@ -14090,7 +14090,7 @@
       </c>
       <c r="DD18" t="inlineStr">
         <is>
-          <t>29.42</t>
+          <t>28.99</t>
         </is>
       </c>
       <c r="DE18" t="inlineStr">
@@ -14105,12 +14105,12 @@
       </c>
       <c r="DG18" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>22.17</t>
         </is>
       </c>
       <c r="DH18" t="inlineStr">
         <is>
-          <t>57360</t>
+          <t>56512</t>
         </is>
       </c>
       <c r="DI18" t="inlineStr">
@@ -14130,22 +14130,22 @@
       </c>
       <c r="DL18" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="DM18" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="DN18" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="DO18" t="inlineStr">
         <is>
-          <t>62.1</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="DP18" t="inlineStr">
@@ -14347,12 +14347,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>6537.907</t>
+          <t>5366.395</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -14362,7 +14362,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>62.1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -14372,17 +14372,17 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -14477,24 +14477,24 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
           <t>弱勢</t>
         </is>
       </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>弱勢</t>
-        </is>
-      </c>
       <c r="AI19" t="inlineStr">
         <is>
           <t>75.0</t>
@@ -14557,12 +14557,12 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>-879326.0</t>
+          <t>3063402.0</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
@@ -14572,17 +14572,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -14662,72 +14662,72 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>51</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>4949</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.9</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>63.38</t>
+          <t>63.39</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>65.03</t>
+          <t>65.06</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>-0.009271099744245448</t>
+          <t>-0.00354953210713127</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
         <is>
-          <t>-0.00518949520364842</t>
+          <t>-0.003635788808093565</t>
         </is>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>-0.002439600220351168</t>
+          <t>7.888923950782889e-05</t>
         </is>
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>-56.43</t>
+          <t>-40.48</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
@@ -14737,7 +14737,7 @@
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
@@ -14747,37 +14747,37 @@
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>1664151582.530137</t>
+          <t>1660823897.512295</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
         <is>
-          <t>398395838.0</t>
+          <t>332395909.0</t>
         </is>
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>321752025.0</t>
+          <t>339059880.6</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
         <is>
-          <t>407191342.6</t>
+          <t>409533935.4</t>
         </is>
       </c>
       <c r="CK19" t="inlineStr">
         <is>
-          <t>532039367.7666667</t>
+          <t>517834921.1666667</t>
         </is>
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>1642748570.1</t>
+          <t>1623092805.68</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>-153996581.9480907</t>
+          <t>-142101585.2845038</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -14792,7 +14792,7 @@
       </c>
       <c r="CP19" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>19.42</t>
         </is>
       </c>
       <c r="CQ19" t="inlineStr">
@@ -14837,7 +14837,7 @@
       </c>
       <c r="CY19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CZ19" t="inlineStr">
@@ -14847,12 +14847,12 @@
       </c>
       <c r="DA19" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="DB19" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="DC19" t="inlineStr">
@@ -14862,7 +14862,7 @@
       </c>
       <c r="DD19" t="inlineStr">
         <is>
-          <t>29.42</t>
+          <t>28.99</t>
         </is>
       </c>
       <c r="DE19" t="inlineStr">
@@ -14877,12 +14877,12 @@
       </c>
       <c r="DG19" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>22.17</t>
         </is>
       </c>
       <c r="DH19" t="inlineStr">
         <is>
-          <t>57360</t>
+          <t>56512</t>
         </is>
       </c>
       <c r="DI19" t="inlineStr">
@@ -14902,22 +14902,22 @@
       </c>
       <c r="DL19" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="DM19" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="DN19" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="DO19" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>62.1</t>
         </is>
       </c>
       <c r="DP19" t="inlineStr">
